--- a/data/trans_orig/IP17-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP17-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8506</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17991</t>
+          <t>17435</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,47 +748,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>15,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>33,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>14766</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9743</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>20804</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>24,52%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>16,18%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>34,22%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>14766</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>9926</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>21041</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>24,52%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>16,48%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20634</t>
+          <t>21469</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35723</t>
+          <t>35101</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34577</t>
+          <t>35133</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44062</t>
+          <t>44212</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,49 +861,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>84,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>45451</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>39413</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>50474</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>75,48%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>65,45%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>83,82%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>45451</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>39176</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>50291</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>75,48%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>65,06%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>83,52%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>128</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77062</t>
+          <t>77684</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92151</t>
+          <t>91316</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>80,96%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7589</t>
+          <t>7843</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18355</t>
+          <t>18028</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13347</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25637</t>
+          <t>26343</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23803</t>
+          <t>23827</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40427</t>
+          <t>39738</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83207</t>
+          <t>83534</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93973</t>
+          <t>93719</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83120</t>
+          <t>82414</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95410</t>
+          <t>95630</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>169892</t>
+          <t>170581</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>186516</t>
+          <t>186492</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,67%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>10289</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22204</t>
+          <t>22042</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13746</t>
+          <t>13190</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25018</t>
+          <t>24893</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26061</t>
+          <t>25805</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42401</t>
+          <t>41779</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45393</t>
+          <t>45555</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57438</t>
+          <t>57308</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45309</t>
+          <t>45434</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56581</t>
+          <t>57137</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>95523</t>
+          <t>96145</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111863</t>
+          <t>112119</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,29%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13641</t>
+          <t>13475</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25481</t>
+          <t>25424</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13686</t>
+          <t>13769</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26891</t>
+          <t>26503</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30557</t>
+          <t>29743</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47876</t>
+          <t>46661</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49380</t>
+          <t>49437</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61220</t>
+          <t>61386</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52220</t>
+          <t>52608</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65425</t>
+          <t>65342</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>106096</t>
+          <t>107311</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>123415</t>
+          <t>124229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,68%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12292</t>
+          <t>12536</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10679</t>
+          <t>10450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19863</t>
+          <t>19547</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29560</t>
+          <t>29316</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37893</t>
+          <t>37857</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34164</t>
+          <t>34393</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42022</t>
+          <t>42009</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66832</t>
+          <t>67148</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78285</t>
+          <t>77668</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>89,59%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17140</t>
+          <t>16884</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14865</t>
+          <t>14096</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15184</t>
+          <t>14729</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28437</t>
+          <t>29182</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38915</t>
+          <t>39171</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48909</t>
+          <t>48678</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44867</t>
+          <t>45636</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53980</t>
+          <t>54166</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>87350</t>
+          <t>86605</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100603</t>
+          <t>101058</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,28%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25232</t>
+          <t>25652</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41674</t>
+          <t>41071</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29506</t>
+          <t>30077</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46869</t>
+          <t>46282</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58189</t>
+          <t>59993</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>82263</t>
+          <t>83340</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>86948</t>
+          <t>87551</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>103390</t>
+          <t>102970</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>88786</t>
+          <t>89373</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>106149</t>
+          <t>105578</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>182014</t>
+          <t>180937</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>206088</t>
+          <t>204284</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15897</t>
+          <t>16078</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29747</t>
+          <t>29821</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27948</t>
+          <t>27751</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45489</t>
+          <t>44950</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>47923</t>
+          <t>48189</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>69884</t>
+          <t>69337</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>128157</t>
+          <t>128083</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>142007</t>
+          <t>141826</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>118569</t>
+          <t>119108</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>136110</t>
+          <t>136307</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>252078</t>
+          <t>252625</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>274039</t>
+          <t>273773</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,03%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>116961</t>
+          <t>116903</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>149439</t>
+          <t>151293</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>143277</t>
+          <t>143533</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>179505</t>
+          <t>179665</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>271234</t>
+          <t>272281</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>317509</t>
+          <t>320747</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>531582</t>
+          <t>529728</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>564060</t>
+          <t>564118</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>543195</t>
+          <t>543035</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>579423</t>
+          <t>579167</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1086212</t>
+          <t>1082974</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1132487</t>
+          <t>1131440</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,6%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>9477</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19934</t>
+          <t>20031</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13004</t>
+          <t>13487</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25821</t>
+          <t>25753</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24991</t>
+          <t>25627</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41306</t>
+          <t>43033</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37493</t>
+          <t>37396</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48269</t>
+          <t>47950</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38988</t>
+          <t>39056</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51805</t>
+          <t>51322</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80930</t>
+          <t>79203</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97245</t>
+          <t>96609</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,03%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20885</t>
+          <t>20727</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35409</t>
+          <t>35115</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22385</t>
+          <t>22378</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37804</t>
+          <t>37605</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46953</t>
+          <t>48196</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68468</t>
+          <t>68562</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69304</t>
+          <t>69598</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83828</t>
+          <t>83986</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73355</t>
+          <t>73554</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>88774</t>
+          <t>88781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147404</t>
+          <t>147310</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>168919</t>
+          <t>167676</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>77,67%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14620</t>
+          <t>14139</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26959</t>
+          <t>26573</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13959</t>
+          <t>15081</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27318</t>
+          <t>28182</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31292</t>
+          <t>32551</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49416</t>
+          <t>49965</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>36,01%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40544</t>
+          <t>40930</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52883</t>
+          <t>53364</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43936</t>
+          <t>43072</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57295</t>
+          <t>56173</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89341</t>
+          <t>88792</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>107465</t>
+          <t>106206</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>76,54%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12780</t>
+          <t>13223</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25954</t>
+          <t>25742</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10832</t>
+          <t>11120</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23205</t>
+          <t>23319</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27998</t>
+          <t>27024</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44001</t>
+          <t>43882</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51044</t>
+          <t>51256</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64218</t>
+          <t>63775</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58028</t>
+          <t>57914</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70401</t>
+          <t>70113</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>114230</t>
+          <t>114349</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>130233</t>
+          <t>131207</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,92%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18234</t>
+          <t>17738</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16341</t>
+          <t>16659</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16629</t>
+          <t>17123</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31156</t>
+          <t>31314</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25667</t>
+          <t>26163</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36907</t>
+          <t>36474</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30411</t>
+          <t>30093</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39873</t>
+          <t>39544</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59497</t>
+          <t>59339</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74024</t>
+          <t>73530</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,11%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10768</t>
+          <t>11209</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21848</t>
+          <t>22525</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10501</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21721</t>
+          <t>21999</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23601</t>
+          <t>24674</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39886</t>
+          <t>41241</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34137</t>
+          <t>33460</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45217</t>
+          <t>44776</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38524</t>
+          <t>38246</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49925</t>
+          <t>49744</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>76344</t>
+          <t>74989</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>92629</t>
+          <t>91556</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>78,77%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22941</t>
+          <t>22440</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38979</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25256</t>
+          <t>25332</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42277</t>
+          <t>42158</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50961</t>
+          <t>52730</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75301</t>
+          <t>76502</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>99856</t>
+          <t>99739</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>115777</t>
+          <t>116278</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>103462</t>
+          <t>103581</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>120483</t>
+          <t>120407</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>209156</t>
+          <t>207955</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>233496</t>
+          <t>231727</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,46%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17423</t>
+          <t>17793</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32040</t>
+          <t>32088</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16629</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31048</t>
+          <t>32010</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37613</t>
+          <t>37161</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>58702</t>
+          <t>58693</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>132668</t>
+          <t>132620</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>147285</t>
+          <t>146915</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>138969</t>
+          <t>138007</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>153388</t>
+          <t>153132</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>276023</t>
+          <t>276032</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>297112</t>
+          <t>297564</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,9%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>145520</t>
+          <t>145285</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>180809</t>
+          <t>183629</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>151924</t>
+          <t>151532</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>189534</t>
+          <t>188742</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>307151</t>
+          <t>307721</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>360128</t>
+          <t>361743</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>529144</t>
+          <t>526324</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>564433</t>
+          <t>564668</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>561675</t>
+          <t>562467</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>599285</t>
+          <t>599677</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1101034</t>
+          <t>1099419</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1154011</t>
+          <t>1153441</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,94%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11300</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21580</t>
+          <t>21195</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12429</t>
+          <t>12215</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24040</t>
+          <t>23945</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26327</t>
+          <t>26209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41792</t>
+          <t>41956</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35791</t>
+          <t>36176</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46071</t>
+          <t>47083</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39838</t>
+          <t>39933</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51449</t>
+          <t>51663</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79457</t>
+          <t>79293</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94922</t>
+          <t>95040</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,38%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20965</t>
+          <t>21277</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36147</t>
+          <t>35714</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21221</t>
+          <t>21731</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36728</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46069</t>
+          <t>47219</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67528</t>
+          <t>66787</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67104</t>
+          <t>67537</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82286</t>
+          <t>81974</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73555</t>
+          <t>73698</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89062</t>
+          <t>88552</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>146006</t>
+          <t>146747</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>167465</t>
+          <t>166315</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>77,89%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14762</t>
+          <t>14465</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14225</t>
+          <t>14533</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12003</t>
+          <t>11869</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24129</t>
+          <t>24607</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52069</t>
+          <t>52366</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61767</t>
+          <t>61879</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53578</t>
+          <t>53270</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62600</t>
+          <t>62940</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110505</t>
+          <t>110027</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>122631</t>
+          <t>122765</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,18%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16504</t>
+          <t>17187</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30399</t>
+          <t>30452</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>18470</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32672</t>
+          <t>32280</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38976</t>
+          <t>39630</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58444</t>
+          <t>58820</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46562</t>
+          <t>46509</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60457</t>
+          <t>59774</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48512</t>
+          <t>48904</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63152</t>
+          <t>62714</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>99701</t>
+          <t>99325</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119169</t>
+          <t>118515</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>74,94%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15197</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15463</t>
+          <t>15207</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14703</t>
+          <t>14445</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27894</t>
+          <t>27681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28241</t>
+          <t>28096</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37332</t>
+          <t>37360</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30887</t>
+          <t>31143</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40134</t>
+          <t>40362</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>61894</t>
+          <t>62107</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75085</t>
+          <t>75343</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,91%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7763</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17708</t>
+          <t>17356</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16731</t>
+          <t>17039</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16073</t>
+          <t>16416</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31142</t>
+          <t>30549</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36565</t>
+          <t>36917</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46510</t>
+          <t>46842</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41008</t>
+          <t>40700</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51578</t>
+          <t>51534</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80870</t>
+          <t>81463</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>95939</t>
+          <t>95596</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>6643</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17669</t>
+          <t>16960</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20023</t>
+          <t>19681</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17426</t>
+          <t>17341</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33238</t>
+          <t>32388</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>119705</t>
+          <t>120414</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>130387</t>
+          <t>130731</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>123336</t>
+          <t>123678</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>134596</t>
+          <t>134860</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>247495</t>
+          <t>248345</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>263307</t>
+          <t>263392</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27251</t>
+          <t>27288</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43496</t>
+          <t>43344</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23924</t>
+          <t>23877</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40149</t>
+          <t>39718</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53841</t>
+          <t>55323</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>77597</t>
+          <t>77151</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>120075</t>
+          <t>120227</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>136320</t>
+          <t>136283</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>130112</t>
+          <t>130543</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>146337</t>
+          <t>146384</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>256235</t>
+          <t>256681</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>279991</t>
+          <t>278509</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,43%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>128350</t>
+          <t>127645</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>163278</t>
+          <t>161928</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>129406</t>
+          <t>129843</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>164987</t>
+          <t>164378</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>264740</t>
+          <t>266751</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>313988</t>
+          <t>316631</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>539792</t>
+          <t>541142</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>574720</t>
+          <t>575425</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>575870</t>
+          <t>576479</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>611451</t>
+          <t>611014</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1129939</t>
+          <t>1127296</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1179187</t>
+          <t>1177176</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,53%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7439</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18190</t>
+          <t>18823</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8793</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21093</t>
+          <t>20912</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18355</t>
+          <t>19058</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34976</t>
+          <t>35470</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55092</t>
+          <t>54459</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65843</t>
+          <t>66011</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58273</t>
+          <t>58454</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70573</t>
+          <t>70550</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117672</t>
+          <t>117178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>134293</t>
+          <t>133590</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21956</t>
+          <t>21213</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10688</t>
+          <t>10033</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24335</t>
+          <t>24206</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19680</t>
+          <t>19487</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41250</t>
+          <t>39975</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>104883</t>
+          <t>105626</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>120295</t>
+          <t>121535</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>103261</t>
+          <t>103390</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>116908</t>
+          <t>117563</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>213185</t>
+          <t>214460</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>234755</t>
+          <t>234948</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,34%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9141</t>
+          <t>9398</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19189</t>
+          <t>19035</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11448</t>
+          <t>10779</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23151</t>
+          <t>22526</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23405</t>
+          <t>23912</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38518</t>
+          <t>38839</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,96%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39079</t>
+          <t>39233</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49127</t>
+          <t>48870</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44012</t>
+          <t>44637</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55715</t>
+          <t>56384</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86913</t>
+          <t>86592</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102026</t>
+          <t>101519</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7839</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7326</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24341</t>
+          <t>23791</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18233</t>
+          <t>18997</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39642</t>
+          <t>39587</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50444</t>
+          <t>50364</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62304</t>
+          <t>62358</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53793</t>
+          <t>54343</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70808</t>
+          <t>71305</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>108636</t>
+          <t>108691</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>130045</t>
+          <t>129281</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,19%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7159</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9640</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14229</t>
+          <t>14579</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27354</t>
+          <t>27366</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32862</t>
+          <t>32799</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31079</t>
+          <t>31406</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37964</t>
+          <t>38257</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>61003</t>
+          <t>60653</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69691</t>
+          <t>69724</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,68%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5354</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13358</t>
+          <t>13809</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11856</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22735</t>
+          <t>22287</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19935</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33689</t>
+          <t>34420</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32809</t>
+          <t>32358</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40813</t>
+          <t>40603</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33451</t>
+          <t>33899</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44330</t>
+          <t>44251</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68664</t>
+          <t>67933</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>82418</t>
+          <t>82229</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,34%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>15767</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33447</t>
+          <t>32374</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19398</t>
+          <t>19590</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37630</t>
+          <t>38867</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39247</t>
+          <t>38726</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64052</t>
+          <t>63081</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>91061</t>
+          <t>92134</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>108856</t>
+          <t>108741</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>118382</t>
+          <t>117145</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>136614</t>
+          <t>136422</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>216468</t>
+          <t>217439</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>241273</t>
+          <t>241794</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,19%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7720</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17865</t>
+          <t>17913</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>13799</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29138</t>
+          <t>28375</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23980</t>
+          <t>24164</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42061</t>
+          <t>41905</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>113754</t>
+          <t>113706</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>123899</t>
+          <t>123875</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>127657</t>
+          <t>128420</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>142699</t>
+          <t>142996</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>246353</t>
+          <t>246509</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>264434</t>
+          <t>264250</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>83926</t>
+          <t>82080</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>120598</t>
+          <t>116826</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>113277</t>
+          <t>113296</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>149728</t>
+          <t>151520</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13501,7 +13501,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>206386</t>
+          <t>207822</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>259768</t>
+          <t>258123</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>544742</t>
+          <t>548514</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>581414</t>
+          <t>583260</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>612244</t>
+          <t>610452</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>648695</t>
+          <t>648676</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1167544</t>
+          <t>1169189</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1220926</t>
+          <t>1219490</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,44%</t>
         </is>
       </c>
     </row>
